--- a/语音/异常投退操作.xlsx
+++ b/语音/异常投退操作.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="89">
   <si>
     <t>序号</t>
   </si>
@@ -68,10 +68,10 @@
     <t>操作完成</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置指示灯，“故障”“熔丝熔断”“硅柜限制”指示灯亮红灯</t>
-  </si>
-  <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置指示灯</t>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置指示灯，“故障”“熔丝熔断”“硅柜限制”指示灯亮红灯</t>
+  </si>
+  <si>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置指示灯</t>
   </si>
   <si>
     <t>“故障”“熔丝熔断”“硅柜限制”指示灯亮红灯</t>
@@ -104,10 +104,10 @@
     <t>已完成可控硅2号整流柜面板表计检查</t>
   </si>
   <si>
-    <t>使用可控硅2号整流柜PCS-9425整流桥智能测控装置，启动双风机，使用右侧键盘选择菜单，命令路径：定值设置，辅助控制定值，风机启动模式，启动双风机以避免检修1号机期间，负载全部转移到2号机，导致2号机过热。</t>
-  </si>
-  <si>
-    <t>使用可控硅2号整流柜PCS-9425整流桥智能测控装置，启动双风机</t>
+    <t>使用可控硅2号整流柜，PCS-9425整流桥智能测控装置，启动双风机，使用右侧键盘选择菜单，命令路径：定值设置，辅助控制定值，风机启动模式，启动双风机以避免检修1号机期间，负载全部转移到2号机，导致2号机过热。</t>
+  </si>
+  <si>
+    <t>使用可控硅2号整流柜，PCS-9425整流桥智能测控装置，启动双风机</t>
   </si>
   <si>
     <t>使用右侧键盘选择菜单，命令路径：定值设置，辅助控制定值，风机启动模式，启动双风机以避免检修1号机期间，负载全部转移到2号机，导致2号机过热。</t>
@@ -116,10 +116,10 @@
     <t>已完成可控硅2号整流柜双风机启动操作</t>
   </si>
   <si>
-    <t>使用可控硅1号整流柜PCS-9425整流桥智能测控装置，执行退柜操作，使用右侧键盘选择菜单，退柜命令路径：定值设置，功能软压板，定值切脉冲</t>
-  </si>
-  <si>
-    <t>使用可控硅1号整流柜PCS-9425整流桥智能测控装置，执行退柜操作</t>
+    <t>使用可控硅1号整流柜，PCS-9425整流桥智能测控装置，执行退柜操作，使用右侧键盘选择菜单，退柜命令路径：定值设置，功能软压板，定值切脉冲</t>
+  </si>
+  <si>
+    <t>使用可控硅1号整流柜，PCS-9425整流桥智能测控装置，执行退柜操作</t>
   </si>
   <si>
     <t>使用右侧键盘选择菜单，退柜命令路径：定值设置，功能软压板，定值切脉冲</t>
@@ -134,27 +134,18 @@
     <t>已打开可控硅1号整流柜柜门</t>
   </si>
   <si>
-    <t>将风机电源空气开关分闸</t>
+    <t>将风机各电源空气开关分闸</t>
   </si>
   <si>
     <t>风机电源空气开关分闸</t>
   </si>
   <si>
-    <t>将风机备用电源空气开关分闸</t>
-  </si>
-  <si>
     <t>风机备用电源空气开关分闸</t>
   </si>
   <si>
-    <t>将交流电源空气开关分闸</t>
-  </si>
-  <si>
     <t>交流电源空气开关分闸</t>
   </si>
   <si>
-    <t>将直流电源空气开关分闸</t>
-  </si>
-  <si>
     <t>直流电源空气开关分闸</t>
   </si>
   <si>
@@ -185,6 +176,12 @@
     <t>检查快熔是否熔断</t>
   </si>
   <si>
+    <t>已完成快熔熔断检测</t>
+  </si>
+  <si>
+    <t>发现Fa快熔熔断</t>
+  </si>
+  <si>
     <t>本次模拟中，假设Fa快熔熔断引发的熔丝故障</t>
   </si>
   <si>
@@ -212,34 +209,25 @@
     <t>已关闭可控硅1号整流柜后柜门</t>
   </si>
   <si>
-    <t>将风机电源空气开关合闸</t>
+    <t>将风机各电源空气开关合闸</t>
   </si>
   <si>
     <t>风机电源空气开关合闸</t>
   </si>
   <si>
-    <t>将风机备用电源空气开关合闸</t>
-  </si>
-  <si>
     <t>风机备用电源空气开关合闸</t>
   </si>
   <si>
-    <t>将交流电源空气开关合闸</t>
-  </si>
-  <si>
     <t>交流电源空气开关合闸</t>
   </si>
   <si>
-    <t>将直流电源空气开关合闸</t>
-  </si>
-  <si>
     <t>直流电源空气开关合闸</t>
   </si>
   <si>
-    <t>使用可控硅1号整流柜PCS-9425整流桥智能测控装置完成故障复位操作，使用右侧键盘选择菜单，故障归复命令路径：本地命令，故障复位</t>
-  </si>
-  <si>
-    <t>使用可控硅1号整流柜PCS-9425整流桥智能测控装置完成故障复位操作</t>
+    <t>使用可控硅1号整流柜，PCS-9425整流桥智能测控装置，完成故障复位操作，使用右侧键盘选择菜单，故障归复命令路径：本地命令，故障复位</t>
+  </si>
+  <si>
+    <t>使用可控硅1号整流柜，PCS-9425整流桥智能测控装置完成故障复位操作</t>
   </si>
   <si>
     <t>使用右侧键盘选择菜单，故障归复命令路径：本地命令，故障复位</t>
@@ -257,10 +245,10 @@
     <t>已完成可控硅1号整流柜面板指示灯检查</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置，“故障”“熔丝熔断”“硅柜限制”指示灯熄灭</t>
-  </si>
-  <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置</t>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置，“故障”“熔丝熔断”“硅柜限制”指示灯熄灭</t>
+  </si>
+  <si>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置</t>
   </si>
   <si>
     <t>“故障”“熔丝熔断”“硅柜限制”指示灯熄灭</t>
@@ -269,10 +257,10 @@
     <t>整流柜快熔熔断故障信号已消除</t>
   </si>
   <si>
-    <t>使用可控硅1号整流柜PCS-9425整流桥智能测控装置完成智能均流投入操作，使用右侧键盘选择菜单，智能均流投入命令路径：定值设置，功能软压板，智能均流投入</t>
-  </si>
-  <si>
-    <t>使用可控硅1号整流柜PCS-9425整流桥智能测控装置完成智能均流投入操作</t>
+    <t>使用可控硅1号整流柜，PCS-9425整流桥智能测控装置，完成智能均流投入操作，使用右侧键盘选择菜单，智能均流投入命令路径：定值设置，功能软压板，智能均流投入</t>
+  </si>
+  <si>
+    <t>使用可控硅1号整流柜，PCS-9425整流桥智能测控装置，完成智能均流投入操作</t>
   </si>
   <si>
     <t>使用右侧键盘选择菜单，智能均流投入命令路径：定值设置，功能软压板，智能均流投入</t>
@@ -281,10 +269,10 @@
     <t>已完成智能均流投入操作</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜面板表计，可控硅1号整流柜二级限制已解除，直流输出恢复至200安，与上位机一致</t>
-  </si>
-  <si>
-    <t>可控硅1号整流柜二级限制已解除，直流输出恢复至200安，与上位机一致</t>
+    <t>检查可控硅1号整流柜面板表计，可控硅1号整流柜二级限制已解除，直流输出恢复至200安</t>
+  </si>
+  <si>
+    <t>可控硅1号整流柜二级限制已解除，直流输出恢复至200安</t>
   </si>
   <si>
     <t>检查可控硅2号整流柜面板表计，可控硅2号整流柜直流输出恢复至200安</t>
@@ -293,16 +281,19 @@
     <t>可控硅2号整流柜直流输出恢复至200安</t>
   </si>
   <si>
-    <t>使用可控硅2号整流柜PCS-9425整流桥智能测控装置，风机启动模式切换回轮换，使用右侧键盘选择菜单，命令路径：定值设置，辅助控制定值，风机启动模式</t>
-  </si>
-  <si>
-    <t>使用可控硅2号整流柜PCS-9425整流桥智能测控装置，风机启动模式切换回轮换</t>
+    <t>已完成整流柜异常投退任务</t>
+  </si>
+  <si>
+    <t>使用可控硅2号整流柜，PCS-9425整流桥智能测控装置，风机启动模式切换回轮换，使用右侧键盘选择菜单，命令路径：定值设置，辅助控制定值，风机启动模式</t>
+  </si>
+  <si>
+    <t>使用可控硅2号整流柜，PCS-9425整流桥智能测控装置，风机启动模式切换回轮换</t>
   </si>
   <si>
     <t>使用右侧键盘选择菜单，命令路径：定值设置，辅助控制定值，风机启动模式</t>
   </si>
   <si>
-    <t>已完成整流柜异常投退任务</t>
+    <t>已完成风机启动模式切换</t>
   </si>
 </sst>
 </file>
@@ -936,7 +927,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -946,6 +937,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1330,7 +1327,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.0083333333333" customWidth="1"/>
@@ -1675,22 +1672,20 @@
     </row>
     <row r="25" ht="30.5" customHeight="1" spans="1:5">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" ht="30.5" customHeight="1" spans="1:5">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
@@ -1703,358 +1698,350 @@
     </row>
     <row r="27" ht="30.5" customHeight="1" spans="1:5">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="30.5" customHeight="1" spans="1:5">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="D28" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="30.5" customHeight="1" spans="1:5">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" ht="30.5" customHeight="1" spans="1:5">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="D30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" ht="30.5" customHeight="1" spans="1:5">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" ht="30.5" customHeight="1" spans="1:5">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="D32" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="30.5" customHeight="1" spans="1:5">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
         <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" ht="30.5" customHeight="1" spans="1:5">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="D34" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" ht="30.5" customHeight="1" spans="1:5">
       <c r="A35" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" ht="30.5" customHeight="1" spans="1:5">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
+      <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
+      <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" ht="30.5" customHeight="1" spans="1:5">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" ht="30.5" customHeight="1" spans="1:5">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2"/>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="D40" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" ht="30.5" customHeight="1" spans="1:5">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" ht="30.5" customHeight="1" spans="1:5">
       <c r="A42" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="3"/>
+      <c r="C42" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="D42" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" ht="30.5" customHeight="1" spans="1:5">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2"/>
-      <c r="C43" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="C43" s="3"/>
       <c r="D43" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" ht="30.5" customHeight="1" spans="1:5">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="3"/>
+      <c r="C44" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="D44" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" ht="30.5" customHeight="1" spans="1:5">
       <c r="A45" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" ht="30.5" customHeight="1" spans="1:5">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="3"/>
+      <c r="C46" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D46" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" ht="30.5" customHeight="1" spans="1:5">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" ht="30.5" customHeight="1" spans="1:5">
       <c r="A48" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2"/>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D48" s="3" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" ht="30.5" customHeight="1" spans="1:5">
       <c r="A49" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" ht="30.5" customHeight="1" spans="1:5">
       <c r="A50" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="3"/>
+      <c r="C50" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="D50" s="3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" ht="30.5" customHeight="1" spans="1:5">
       <c r="A51" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2"/>
-      <c r="C51" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" ht="30.5" customHeight="1" spans="1:5">
       <c r="A52" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="3"/>
@@ -2067,22 +2054,20 @@
     </row>
     <row r="53" ht="30.5" customHeight="1" spans="1:5">
       <c r="A53" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" ht="30.5" customHeight="1" spans="1:5">
       <c r="A54" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="3"/>
@@ -2095,14 +2080,14 @@
     </row>
     <row r="55" ht="30.5" customHeight="1" spans="1:5">
       <c r="A55" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="3" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>2</v>
@@ -2110,91 +2095,89 @@
     </row>
     <row r="56" ht="30.5" customHeight="1" spans="1:5">
       <c r="A56" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="57" ht="30.5" customHeight="1" spans="1:5">
+    <row r="57" ht="63.5" customHeight="1" spans="1:5">
       <c r="A57" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="58" ht="30.5" customHeight="1" spans="1:5">
+    <row r="58" ht="47" customHeight="1" spans="1:5">
       <c r="A58" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" ht="30.5" customHeight="1" spans="1:5">
       <c r="A59" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" ht="30.5" customHeight="1" spans="1:5">
       <c r="A60" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B60" s="2"/>
-      <c r="C60" s="3"/>
+      <c r="C60" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="D60" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" ht="63.5" customHeight="1" spans="1:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" ht="30.5" customHeight="1" spans="1:5">
       <c r="A61" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B61" s="2"/>
-      <c r="C61" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" ht="47" customHeight="1" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" ht="30.5" customHeight="1" spans="1:5">
       <c r="A62" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="3"/>
@@ -2202,265 +2185,219 @@
         <v>71</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" ht="47" customHeight="1" spans="1:5">
       <c r="A63" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="3"/>
+      <c r="C63" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D63" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" ht="30.5" customHeight="1" spans="1:5">
       <c r="A64" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B64" s="2"/>
-      <c r="C64" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="C64" s="3"/>
       <c r="D64" s="3" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" ht="30.5" customHeight="1" spans="1:5">
       <c r="A65" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" ht="63.5" customHeight="1" spans="1:5">
       <c r="A66" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B66" s="2"/>
-      <c r="C66" s="3"/>
+      <c r="C66" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="D66" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" ht="47" customHeight="1" spans="1:5">
       <c r="A67" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B67" s="2"/>
-      <c r="C67" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" ht="30.5" customHeight="1" spans="1:5">
       <c r="A68" s="2">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" ht="30.5" customHeight="1" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" ht="63.5" customHeight="1" spans="1:5">
       <c r="A69" s="2">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B69" s="2"/>
-      <c r="C69" s="3"/>
+      <c r="C69" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="D69" s="3" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" ht="63.5" customHeight="1" spans="1:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" ht="47" customHeight="1" spans="1:5">
       <c r="A70" s="2">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B70" s="2"/>
-      <c r="C70" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" ht="47" customHeight="1" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" ht="30.5" customHeight="1" spans="1:5">
       <c r="A71" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" ht="47" customHeight="1" spans="1:5">
+      <c r="A72" s="2">
+        <v>75</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="D72" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" ht="47" customHeight="1" spans="1:5">
+      <c r="A73" s="2">
+        <v>76</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A72" s="2">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" ht="63.5" customHeight="1" spans="1:5">
-      <c r="A73" s="2">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="3" t="s">
+    <row r="74" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A74" s="2">
+        <v>77</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" ht="47" customHeight="1" spans="1:5">
-      <c r="A74" s="2">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3" t="s">
+      <c r="E74" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A75" s="2">
+        <v>78</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A75" s="2">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" ht="47" customHeight="1" spans="1:5">
       <c r="A76" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B76" s="2"/>
-      <c r="C76" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" ht="47" customHeight="1" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" ht="30.5" customHeight="1" spans="1:5">
       <c r="A77" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="78" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A78" s="2">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3" t="s">
-        <v>24</v>
+    <row r="78" ht="16.5" spans="1:5">
+      <c r="D78" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" ht="63.5" customHeight="1" spans="1:5">
-      <c r="A79" s="2">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" ht="47" customHeight="1" spans="1:5">
-      <c r="A80" s="2">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A81" s="2">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E81" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2468,7 +2405,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B2:E8 B9 D9:E9 B10:C10 E10 B11:E11 B12 D12:E12 B13:C13 E13 B14:E72 B73 D73:E73 B74:C74 E74 B75:E75 B76 D76:E76 B77:C77 E77 B78:E81 A1:E1" numberStoredAsText="1"/>
+    <ignoredError sqref="B7:E8 A1:E1 B72:B77 B71:E71 E70 B70:C70 D69:E69 B69 B67:E68 E66 B66 B64:E65 E63 B63 B58:E62 E57 B57 B51:E56 E50 B50 E36 B36:C36 B24:E35 E23 B23 B19:E22 E18 B18 B16:E17 E15 B15 B14:E14 E13 B13:C13 D12:E12 B12 B11:E11 E10 B10:C10 D9:E9 B9 E6 B6 B2:E5 B40:E49 B39:C39" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>